--- a/data/incremental/incremental_07_la_florida_manual.xlsx
+++ b/data/incremental/incremental_07_la_florida_manual.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Restaurantes" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Restaurantes'!$A$1:$AG$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Restaurantes'!$A$1:$AG$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -425,16 +425,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG27"/>
+  <dimension ref="A1:AG31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="42" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="42" customWidth="1" min="6" max="6"/>
-    <col width="29" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
     <col width="42" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
     <col width="13" customWidth="1" min="10" max="10"/>
@@ -664,7 +664,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Trattoria+Valerio+-+Pizzas+%26+Pastas/@-33.5564369,-70.5865183,17z/data=!3m1!4b1!4m6!3m5!1s0x9662d1b23d025fb7:0x7dbdf26df96b5f4a!8m2!3d-33.5564369!4d-70.5865183!16s%2Fg%2F11h3kchwvb?authuser=0&amp;hl=es-419&amp;entry=ttu&amp;g_ep=EgoyMDI2MDUyMC4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/Trattoria+Valerio+-+Pizzas+%26+Pastas/data=!4m7!3m6!1s0x9662d1b23d025fb7:0x7dbdf26df96b5f4a!8m2!3d-33.5564369!4d-70.5865183!16s%2Fg%2F11h3kchwvb!19sChIJt18CPbLRYpYRSl9r-W3yvX0?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -802,7 +802,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/El+Nomade+Cevicheria/@-33.5534033,-70.5832872,17z/data=!3m1!4b1!4m6!3m5!1s0x9662d12a163492e5:0xa48e479f19d80dcf!8m2!3d-33.5534033!4d-70.5832872!16s%2Fg%2F11s8c5t1wk?authuser=0&amp;hl=es-419&amp;entry=ttu&amp;g_ep=EgoyMDI2MDUyMC4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/El+Nomade+Cevicheria/data=!4m7!3m6!1s0x9662d12a163492e5:0xa48e479f19d80dcf!8m2!3d-33.5534033!4d-70.5832872!16s%2Fg%2F11s8c5t1wk!19sChIJ5ZI0FirRYpYRzw3YGZ9HjqQ?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/CABIMAS+TASTY+FOOD/@-33.5548557,-70.5860092,17z/data=!3m1!4b1!4m6!3m5!1s0x9662d1dacc48255b:0x6d53e79d90e8d33a!8m2!3d-33.5548557!4d-70.5860092!16s%2Fg%2F11vrz4mx5h?authuser=0&amp;hl=es-419&amp;entry=ttu&amp;g_ep=EgoyMDI2MDUyMC4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/CABIMAS+TASTY+FOOD/data=!4m7!3m6!1s0x9662d1dacc48255b:0x6d53e79d90e8d33a!8m2!3d-33.5548557!4d-70.5860092!16s%2Fg%2F11vrz4mx5h!19sChIJWyVIzNrRYpYROtPokJ3nU20?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1144,48 +1144,48 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Aquí E’</t>
+          <t>COCINERIA DONDE YOYO'S</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>07</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Sgto. Candelaria Pérez 10693, 8310309 La Florida, Región Metropolitana</t>
+          <t>Av. La Florida 9233, 8242051 La Florida, Región Metropolitana</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>9 9250 7960</t>
+          <t>9 7354 5215</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Restaurante</t>
+          <t>Restaurante chileno</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Aqu%C3%AD+E%E2%80%99/data=!4m7!3m6!1s0x9662d16caadbd913:0xf4e8696dcf47dc21!8m2!3d-33.5571101!4d-70.5864892!16s%2Fg%2F11s5b_5mdy!19sChIJE9nbqmzRYpYRIdxHz21p6PQ?authuser=0&amp;hl=es-419&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/COCINERIA+DONDE+YOYO%27S/data=!4m7!3m6!1s0x9662d1d95c833fd9:0x3c68e41dd033ed33!8m2!3d-33.5371433!4d-70.5731178!16s%2Fg%2F11p5s69mwx!19sChIJ2T-DXNnRYpYRM-0z0B3kaDw?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-33.5571101</t>
+          <t>-33.5371433</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-70.5864892</t>
+          <t>-70.5731178</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1210,7 +1210,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1243,30 +1243,34 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>La Caleta de Don Chuma</t>
+          <t>Restaurante Punta Brasa La Florida</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>249</t>
+          <t>66</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Av. Vicuña Mackenna 10197, Local 3, La Florida, Región Metropolitana</t>
+          <t>Palena 3152, 8240000 La Florida, Región Metropolitana</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>(2) 2614 5107</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
+          <t>(2) 2669 3751</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>http://www.puntabrasa.cl/</t>
+        </is>
+      </c>
       <c r="G8" t="inlineStr">
         <is>
           <t>Restaurante</t>
@@ -1274,17 +1278,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/La+Caleta+de+Don+Chuma/data=!4m7!3m6!1s0x9662d0c521288777:0x43817670a73eee44!8m2!3d-33.551873!4d-70.587242!16s%2Fg%2F11ddxvpj91!19sChIJd4coIcXQYpYRRO4-p3B2gUM?authuser=0&amp;hl=es-419&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/Restaurante+Punta+Brasa+La+Florida/data=!4m7!3m6!1s0x9662cfa4d8996d17:0xff23c0d1e494ab08!8m2!3d-33.5179138!4d-70.563385!16s%2Fg%2F11s63xjxk7!19sChIJF22Z2KTPYpYRCKuU5NHAI_8?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-33.551873</t>
+          <t>-33.5179138</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-70.587242</t>
+          <t>-70.563385</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1309,12 +1313,12 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Parcial</t>
+          <t>Completo</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -1342,48 +1346,48 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>COCINERIA DONDE YOYO'S</t>
+          <t>La Caleta de Don Chuma</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>249</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Av. La Florida 9233, 8242051 La Florida, Región Metropolitana</t>
+          <t>Av. Vicuña Mackenna 10197, Local 3, La Florida, Región Metropolitana</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>9 7354 5215</t>
+          <t>(2) 2614 5107</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Restaurante chileno</t>
+          <t>Restaurante</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/COCINERIA+DONDE+YOYO%27S/data=!4m7!3m6!1s0x9662d1d95c833fd9:0x3c68e41dd033ed33!8m2!3d-33.5371433!4d-70.5731178!16s%2Fg%2F11p5s69mwx!19sChIJ2T-DXNnRYpYRM-0z0B3kaDw?authuser=0&amp;hl=es-419&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/La+Caleta+de+Don+Chuma/data=!4m7!3m6!1s0x9662d0c521288777:0x43817670a73eee44!8m2!3d-33.551873!4d-70.587242!16s%2Fg%2F11ddxvpj91!19sChIJd4coIcXQYpYRRO4-p3B2gUM?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-33.5371433</t>
+          <t>-33.551873</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-70.5731178</t>
+          <t>-70.587242</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1408,7 +1412,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1441,34 +1445,30 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Restaurante Punta Brasa La Florida</t>
+          <t>Aquí E’</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>69</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Palena 3152, 8240000 La Florida, Región Metropolitana</t>
+          <t>Sgto. Candelaria Pérez 10693, 8310309 La Florida, Región Metropolitana</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>(2) 2669 3751</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>http://www.puntabrasa.cl/</t>
-        </is>
-      </c>
+          <t>9 9250 7960</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
           <t>Restaurante</t>
@@ -1476,17 +1476,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Restaurante+Punta+Brasa+La+Florida/@-33.5179138,-70.563385,17z/data=!3m1!4b1!4m6!3m5!1s0x9662cfa4d8996d17:0xff23c0d1e494ab08!8m2!3d-33.5179138!4d-70.563385!16s%2Fg%2F11s63xjxk7?authuser=0&amp;hl=es-419&amp;entry=ttu&amp;g_ep=EgoyMDI2MDUyMC4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/Aqu%C3%AD+E%E2%80%99/data=!4m7!3m6!1s0x9662d16caadbd913:0xf4e8696dcf47dc21!8m2!3d-33.5571101!4d-70.5864892!16s%2Fg%2F11s5b_5mdy!19sChIJE9nbqmzRYpYRIdxHz21p6PQ?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-33.5179138</t>
+          <t>-33.5571101</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-70.563385</t>
+          <t>-70.5864892</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1511,12 +1511,12 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Completo</t>
+          <t>Parcial</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -1610,7 +1610,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1643,48 +1643,52 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>El Estribo</t>
+          <t>MEGA AJISECO LA FLORIDA 8961</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>31</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Manutara 10606, 8310024 La Florida, Región Metropolitana</t>
+          <t>Av. La Florida 8961, 8241429 La Florida, Región Metropolitana</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>(2) 3341 7737</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
+          <t>9 3104 6615</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>http://www.elajiseco.cl/</t>
+        </is>
+      </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Restaurante</t>
+          <t>Restaurante peruano</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/El+Estribo/data=!4m7!3m6!1s0x9662d133b394bd4f:0xcb13d2321151ca64!8m2!3d-33.5559548!4d-70.5917283!16s%2Fg%2F11g_y5k1md!19sChIJT72UszPRYpYRZMpRETLSE8s?authuser=0&amp;hl=es-419&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/MEGA+AJISECO+LA+FLORIDA+8961/data=!4m7!3m6!1s0x9662d1942458681b:0x2af542540066ebdd!8m2!3d-33.5332063!4d-70.5748729!16s%2Fg%2F11tf8gq63b!19sChIJG2hYJJTRYpYR3etmAFRC9So?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-33.5559548</t>
+          <t>-33.5332063</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-70.5917283</t>
+          <t>-70.5748729</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1709,12 +1713,12 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Parcial</t>
+          <t>Completo</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -1742,52 +1746,48 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>MEGA AJISECO LA FLORIDA 8961</t>
+          <t>El Estribo</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>209</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Av. La Florida 8961, 8241429 La Florida, Región Metropolitana</t>
+          <t>Manutara 10606, 8310024 La Florida, Región Metropolitana</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>9 3104 6615</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>http://www.elajiseco.cl/</t>
-        </is>
-      </c>
+          <t>(2) 3341 7737</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Restaurante peruano</t>
+          <t>Restaurante</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/MEGA+AJISECO+LA+FLORIDA+8961/data=!4m7!3m6!1s0x9662d1942458681b:0x2af542540066ebdd!8m2!3d-33.5332063!4d-70.5748729!16s%2Fg%2F11tf8gq63b!19sChIJG2hYJJTRYpYR3etmAFRC9So?authuser=0&amp;hl=es-419&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/El+Estribo/data=!4m7!3m6!1s0x9662d133b394bd4f:0xcb13d2321151ca64!8m2!3d-33.5559548!4d-70.5917283!16s%2Fg%2F11g_y5k1md!19sChIJT72UszPRYpYRZMpRETLSE8s?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-33.5332063</t>
+          <t>-33.5559548</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-70.5748729</t>
+          <t>-70.5917283</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Completo</t>
+          <t>Parcial</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -1915,7 +1915,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1948,44 +1948,52 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sabrosura</t>
+          <t>Chinito Dice</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>520</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Av. San José de la Estrella 22, parad.23, 8310006 La Florida, Región Metropolitana</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
+          <t>Av. Vicuña Mackenna 10197, La Florida, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>(2) 2282 0462</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>https://flow.page/chinitodice?fbclid=PAZXh0bgNhZW0CMTEAAaaxsw8mGik9E_eBiWJJOUPh7fVcb24HKNgnD4W8RLzQupuUashdMyEfy9w_aem_Mo-6t576wmaFeoljx0EUHw</t>
+        </is>
+      </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hamburguesería</t>
+          <t>Restaurante chino</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Sabrosura/data=!4m7!3m6!1s0x9662d1007e1676b7:0x4631cc0815cc56f7!8m2!3d-33.5532399!4d-70.5861815!16s%2Fg%2F11vr289qz6!19sChIJt3YWfgDRYpYR91bMFQjMMUY?authuser=0&amp;hl=es-419&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/Chinito+Dice/data=!4m7!3m6!1s0x9662d0001977171d:0x967b231f539179fd!8m2!3d-33.5518725!4d-70.5872416!16s%2Fg%2F1thw7yhn!19sChIJHRd3GQDQYpYR_XmRUx8je5Y?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-33.5532399</t>
+          <t>-33.5518725</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-70.5861815</t>
+          <t>-70.5872416</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -2010,17 +2018,17 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Sin teléfono</t>
+          <t>Completo</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="R15" t="inlineStr"/>
@@ -2038,61 +2046,49 @@
       <c r="AD15" t="inlineStr"/>
       <c r="AE15" t="inlineStr"/>
       <c r="AF15" t="inlineStr"/>
-      <c r="AG15" t="inlineStr">
-        <is>
-          <t>Revisar: parece hamburgueseria; Sin teléfono visible</t>
-        </is>
-      </c>
+      <c r="AG15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Chinito Dice</t>
+          <t>Sabrosura</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>520</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Av. Vicuña Mackenna 10197, La Florida, Región Metropolitana</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>(2) 2282 0462</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>https://flow.page/chinitodice?fbclid=PAZXh0bgNhZW0CMTEAAaaxsw8mGik9E_eBiWJJOUPh7fVcb24HKNgnD4W8RLzQupuUashdMyEfy9w_aem_Mo-6t576wmaFeoljx0EUHw</t>
-        </is>
-      </c>
+          <t>Av. San José de la Estrella 22, parad.23, 8310006 La Florida, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Restaurante chino</t>
+          <t>Hamburguesería</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Chinito+Dice/@-33.5518725,-70.5872416,17z/data=!3m1!4b1!4m6!3m5!1s0x9662d0001977171d:0x967b231f539179fd!8m2!3d-33.5518725!4d-70.5872416!16s%2Fg%2F1thw7yhn?authuser=0&amp;hl=es-419&amp;entry=ttu&amp;g_ep=EgoyMDI2MDUyMC4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/Sabrosura/data=!4m7!3m6!1s0x9662d1007e1676b7:0x4631cc0815cc56f7!8m2!3d-33.5532399!4d-70.5861815!16s%2Fg%2F11vr289qz6!19sChIJt3YWfgDRYpYR91bMFQjMMUY?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-33.5518725</t>
+          <t>-33.5532399</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-70.5872416</t>
+          <t>-70.5861815</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -2117,17 +2113,17 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Completo</t>
+          <t>Sin teléfono</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R16" t="inlineStr"/>
@@ -2145,37 +2141,41 @@
       <c r="AD16" t="inlineStr"/>
       <c r="AE16" t="inlineStr"/>
       <c r="AF16" t="inlineStr"/>
-      <c r="AG16" t="inlineStr"/>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>Revisar: parece hamburgueseria; Sin teléfono visible</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>12 Food, La Florida</t>
+          <t>El Zócalo Cocina Mexicana - La Florida</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>309</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Perú 10047, 8240000 La Florida, Región Metropolitana</t>
+          <t>Enrique Olivares 3189, 8290305 La Florida, Región Metropolitana</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>9 5467 2148</t>
+          <t>9 4543 7001</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/12foodlaflorida/?hl=es-la</t>
+          <t>http://www.elzocalo.cl/</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2185,17 +2185,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/12+Food,+La+Florida/@-33.5486896,-70.5831831,17z/data=!3m1!4b1!4m6!3m5!1s0x9662d109cd97fa03:0x2c1e122440b54e76!8m2!3d-33.5486896!4d-70.5831831!16s%2Fg%2F11rwmftnj8?authuser=0&amp;hl=es-419&amp;entry=ttu&amp;g_ep=EgoyMDI2MDUyMC4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/El+Z%C3%B3calo+Cocina+Mexicana+-+La+Florida/data=!4m7!3m6!1s0x9662d1be294a7d55:0xaab20e8c6b122a8c!8m2!3d-33.5400067!4d-70.5596077!16s%2Fg%2F11rpczx24q!19sChIJVX1KKb7RYpYRjCoSa4wOsqo?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-33.5486896</t>
+          <t>-33.5400067</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-70.5831831</t>
+          <t>-70.5596077</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -2220,7 +2220,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Sabor+X2+La+Florida/@-33.5205823,-70.5995334,17z/data=!3m1!4b1!4m6!3m5!1s0x9662d1eb98d949d3:0xed7775e8b16f208!8m2!3d-33.5205823!4d-70.5995334!16s%2Fg%2F11vlxfg6nt?authuser=0&amp;hl=es-419&amp;entry=ttu&amp;g_ep=EgoyMDI2MDUyMC4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/Sabor+X2+La+Florida/data=!4m7!3m6!1s0x9662d1eb98d949d3:0xed7775e8b16f208!8m2!3d-33.5205823!4d-70.5995334!16s%2Fg%2F11vlxfg6nt!19sChIJ00nZmOvRYpYRCPIWi1531w4?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2323,7 +2323,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2356,32 +2356,32 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>El Zócalo Cocina Mexicana - La Florida</t>
+          <t>12 Food, La Florida</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>309</t>
+          <t>89</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Enrique Olivares 3189, 8290305 La Florida, Región Metropolitana</t>
+          <t>Perú 10047, 8240000 La Florida, Región Metropolitana</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>9 4543 7001</t>
+          <t>9 5467 2148</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>http://www.elzocalo.cl/</t>
+          <t>https://www.instagram.com/12foodlaflorida/?hl=es-la</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2391,17 +2391,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/El+Z%C3%B3calo+Cocina+Mexicana+-+La+Florida/data=!4m7!3m6!1s0x9662d1be294a7d55:0xaab20e8c6b122a8c!8m2!3d-33.5400067!4d-70.5596077!16s%2Fg%2F11rpczx24q!19sChIJVX1KKb7RYpYRjCoSa4wOsqo?authuser=0&amp;hl=es-419&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/12+Food,+La+Florida/data=!4m7!3m6!1s0x9662d109cd97fa03:0x2c1e122440b54e76!8m2!3d-33.5486896!4d-70.5831831!16s%2Fg%2F11rwmftnj8!19sChIJA_qXzQnRYpYRdk61QCQSHiw?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-33.5400067</t>
+          <t>-33.5486896</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-70.5596077</t>
+          <t>-70.5831831</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2426,7 +2426,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2459,48 +2459,52 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Nagai Sushi La Florida</t>
+          <t>Restaurant Chilenazo La Florida</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>33</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Av. Vicuña Mackenna Ote. 10706, 8301163 Santiago, La Florida, Región Metropolitana</t>
+          <t>Vicuña Mackenna N° 8855, 8260941 La Florida, Región Metropolitana</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>(2) 2891 8862</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr"/>
+          <t>9 7277 2596</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>https://www.chilenazorestaurant.cl/Locales/la-florida/</t>
+        </is>
+      </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Restaurante de sushi</t>
+          <t>Parrilla</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Nagai+Sushi+La+Florida/data=!4m7!3m6!1s0x9662d0d1d48d902d:0x1e19b02ad00dc61a!8m2!3d-33.556756!4d-70.5856981!16s%2Fg%2F11c37lv_gl!19sChIJLZCN1NHQYpYRGsYN0CqwGR4?authuser=0&amp;hl=es-419&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/Restaurant+Chilenazo+La+Florida/data=!4m7!3m6!1s0x9662d0ec33856031:0x1de315c7437cb08d!8m2!3d-33.5366392!4d-70.5930343!16s%2Fg%2F11bycly77h!19sChIJMWCFM-zQYpYRjbB8Q8cV4x0?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-33.556756</t>
+          <t>-33.5366392</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-70.5856981</t>
+          <t>-70.5930343</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -2525,12 +2529,12 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Parcial</t>
+          <t>Completo</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
@@ -2558,48 +2562,52 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Nosolocrudos</t>
+          <t>Entre Tongoy y La Florida</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Av. San José de la Estrella 297, 8301007 La Florida, Región Metropolitana</t>
+          <t>Av. La Florida 9482, 8301969 La Florida, Región Metropolitana</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>9 6443 5071</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr"/>
+          <t>(2) 3377 4500</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>https://instagram.com/entretongoyylaflorida?igshid=16tosjkz97z3q</t>
+        </is>
+      </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Restaurante de comida cruda</t>
+          <t>Restaurante chileno</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Nosolocrudos/data=!4m7!3m6!1s0x9662d1a4965f2f2f:0xe84eb6faa2050247!8m2!3d-33.5533471!4d-70.5833934!16s%2Fg%2F11h5s1v2g3!19sChIJLy9flqTRYpYRRwIFovq2Tug?authuser=0&amp;hl=es-419&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/Entre+Tongoy+y+La+Florida/data=!4m7!3m6!1s0x9662d11f98ac5843:0x9ab2dcefc1502141!8m2!3d-33.5394957!4d-70.5713781!16s%2Fg%2F1wrglccb!19sChIJQ1ismB_RYpYRQSFQwe_cspo?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-33.5533471</t>
+          <t>-33.5394957</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-70.5833934</t>
+          <t>-70.5713781</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -2624,12 +2632,12 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Parcial</t>
+          <t>Completo</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
@@ -2657,52 +2665,52 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Honua Poke Bar</t>
+          <t>La Pinche Pizza Santa Amalia</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>40</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Av. Las Condes 7134, 7560678 Las Condes, Región Metropolitana</t>
+          <t>Av. La Florida 9660, Local 19, 8301816 La Florida, Región Metropolitana</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>(2) 2884 1768</t>
+          <t>9 4740 1819</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://honuapoke.cl/</t>
+          <t>https://lapinchepizza.cl/</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Restaurante hawaiano</t>
+          <t>Pizzería</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Honua+Poke+Bar/@-33.4044438,-70.5573522,17z/data=!3m1!4b1!4m6!3m5!1s0x9662cf30d24d21fd:0x9717b0273fc65fdd!8m2!3d-33.4044438!4d-70.5573522!16s%2Fg%2F11gfp18h9k?authuser=0&amp;hl=es-419&amp;entry=ttu&amp;g_ep=EgoyMDI2MDUyMC4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/La+Pinche+Pizza+Santa+Amalia/data=!4m7!3m6!1s0x9662d174162c590d:0x6674cdc6f6238622!8m2!3d-33.543272!4d-70.569287!16s%2Fg%2F11xyj30xqs!19sChIJDVksFnTRYpYRIoYj9sbNdGY?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-33.4044438</t>
+          <t>-33.543272</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-70.5573522</t>
+          <t>-70.569287</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -2727,7 +2735,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2760,48 +2768,52 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>MANGIARE PIZZERÍA</t>
+          <t>Restaurant Parrilladas Bright Gran Avenida La Cisterna</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>478</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Gerónimo de Alderete 1742, 8241826 La Florida, Región Metropolitana</t>
+          <t>Gran Av. José Miguel Carrera 8455, 7970653 La Cisterna, Región Metropolitana</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>9 3245 8957</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr"/>
+          <t>9 6566 7616</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>http://parrilladasbright.cl/</t>
+        </is>
+      </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pizzería</t>
+          <t>Restaurante</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/MANGIARE+PIZZER%C3%8DA/@-33.52863,-70.5769358,17z/data=!3m1!4b1!4m6!3m5!1s0x9662d100060aba73:0x414e9e323b635b0c!8m2!3d-33.52863!4d-70.5769358!16s%2Fg%2F11yfmrcxkm?authuser=0&amp;hl=es-419&amp;entry=ttu&amp;g_ep=EgoyMDI2MDUyMC4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/Restaurant+Parrilladas+Bright+Gran+Avenida+La+Cisterna/data=!4m7!3m6!1s0x9662da55e0a57aaf:0x6afabd9b4eaa2fe6!8m2!3d-33.532585!4d-70.663244!16s%2Fg%2F1th834m9!19sChIJr3ql4FXaYpYR5i-qTpu9-mo?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-33.52863</t>
+          <t>-33.532585</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-70.5769358</t>
+          <t>-70.663244</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2826,12 +2838,12 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Parcial</t>
+          <t>Completo</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
@@ -2859,52 +2871,48 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Restaurant Chilenazo La Florida</t>
+          <t>Glotón Lucho</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>38</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Vicuña Mackenna N° 8855, 8260941 La Florida, Región Metropolitana</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>9 7277 2596</t>
-        </is>
-      </c>
+          <t>Samurai 1388, 8242116 La Florida, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://www.chilenazorestaurant.cl/Locales/la-florida/</t>
+          <t>https://www.instagram.com/gloton_lucho</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Parrilla</t>
+          <t>Restaurante de comida rápida</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Restaurant+Chilenazo+La+Florida/@-33.5366392,-70.5930343,17z/data=!3m1!4b1!4m6!3m5!1s0x9662d0ec33856031:0x1de315c7437cb08d!8m2!3d-33.5366392!4d-70.5930343!16s%2Fg%2F11bycly77h?authuser=0&amp;hl=es-419&amp;entry=ttu&amp;g_ep=EgoyMDI2MDUyMC4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/Glot%C3%B3n+Lucho/data=!4m7!3m6!1s0x9662d059a2125861:0x4901ce20cf8fb989!8m2!3d-33.5180395!4d-70.5887574!16s%2Fg%2F1th1dy80!19sChIJYVgSolnQYpYRibmPzyDOAUk?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>-33.5366392</t>
+          <t>-33.5180395</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>-70.5930343</t>
+          <t>-70.5887574</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -2929,12 +2937,12 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Completo</t>
+          <t>Sin teléfono</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
@@ -2957,53 +2965,61 @@
       <c r="AD24" t="inlineStr"/>
       <c r="AE24" t="inlineStr"/>
       <c r="AF24" t="inlineStr"/>
-      <c r="AG24" t="inlineStr"/>
+      <c r="AG24" t="inlineStr">
+        <is>
+          <t>Revisar: parece comida rapida; Sin teléfono visible</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Restaurante Xing Yun</t>
+          <t>Kaitona Sushi la Florida</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>62</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Av. San José de la Estrella 501, 8300968 La Florida, Región Metropolitana</t>
+          <t>Los Barquitos 21, 8240000 La Florida, Región Metropolitana</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>(2) 2318 4758</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr"/>
+          <t>9 3084 4686</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>http://kaitonasushi.cl/</t>
+        </is>
+      </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Restaurante cantonés</t>
+          <t>Restaurante de sushi</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Restaurante+Xing+Yun/data=!4m7!3m6!1s0x9662d0c571140129:0xe09058224870ea25!8m2!3d-33.5532257!4d-70.5807912!16s%2Fg%2F11f122bkxz!19sChIJKQEUccXQYpYRJepwSCJYkOA?authuser=0&amp;hl=es-419&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/Kaitona+Sushi+la+Florida/data=!4m7!3m6!1s0x9662d1f76ec1b7a5:0x725980771689b33f!8m2!3d-33.5528775!4d-70.587246!16s%2Fg%2F11wbnvntzc!19sChIJpbfBbvfRYpYRP7OJFneAWXI?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>-33.5532257</t>
+          <t>-33.5528775</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>-70.5807912</t>
+          <t>-70.587246</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -3028,12 +3044,12 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Parcial</t>
+          <t>Completo</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
@@ -3061,52 +3077,48 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Sweet &amp; Salty</t>
+          <t>Nagai Sushi La Florida</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>115</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Jardín Alto 9562, 8290281 La Florida, Región Metropolitana</t>
+          <t>Av. Vicuña Mackenna Ote. 10706, 8301163 Santiago, La Florida, Región Metropolitana</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>9 9651 2939</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>https://menu.fu.do/sweet&amp;salty</t>
-        </is>
-      </c>
+          <t>(2) 2891 8862</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pub restaurante</t>
+          <t>Restaurante de sushi</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Sweet+%26+Salty/@-33.5400375,-70.5560127,17z/data=!3m1!4b1!4m6!3m5!1s0x9662d13e769226a5:0xe5f7b987c74bf725!8m2!3d-33.5400375!4d-70.5560127!16s%2Fg%2F11dfhxw_xl?authuser=0&amp;hl=es-419&amp;entry=ttu&amp;g_ep=EgoyMDI2MDUyMC4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/Nagai+Sushi+La+Florida/data=!4m7!3m6!1s0x9662d0d1d48d902d:0x1e19b02ad00dc61a!8m2!3d-33.556756!4d-70.5856981!16s%2Fg%2F11c37lv_gl!19sChIJLZCN1NHQYpYRGsYN0CqwGR4?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>-33.5400375</t>
+          <t>-33.556756</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>-70.5560127</t>
+          <t>-70.5856981</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -3131,12 +3143,12 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Completo</t>
+          <t>Parcial</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
@@ -3164,52 +3176,48 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>El Hoyo</t>
+          <t>Byron Sanguchería - Carrito - Comida Rápida 24/7</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>366</t>
+          <t>42</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Froilán Roa 7205, 8240000 La Florida, Región Metropolitana</t>
+          <t>Av. La Florida 10271, La Florida, Región Metropolitana</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>9 4790 0994</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>https://elhoyo1912.cl/</t>
-        </is>
-      </c>
+          <t>9 6272 4353</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Restaurante chileno</t>
+          <t>Restaurante</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/El+Hoyo/data=!4m7!3m6!1s0x9662d1cf3385455d:0xe395a204c2c76415!8m2!3d-33.5171712!4d-70.5972765!16s%2Fg%2F11sv720cml!19sChIJXUWFM8_RYpYRFWTHwgSileM?authuser=0&amp;hl=es-419&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/Byron+Sangucher%C3%ADa+-+Carrito+-+Comida+R%C3%A1pida+24%2F7/data=!4m7!3m6!1s0x9662d12f77a823e7:0xfb5b847b8e87d9ac!8m2!3d-33.5514958!4d-70.565436!16s%2Fg%2F11clv7dx_2!19sChIJ5yOody_RYpYRrNmHjnuEW_s?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>-33.5171712</t>
+          <t>-33.5514958</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>-70.5972765</t>
+          <t>-70.565436</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -3234,12 +3242,12 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Completo</t>
+          <t>Parcial</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
@@ -3262,10 +3270,422 @@
       <c r="AD27" t="inlineStr"/>
       <c r="AE27" t="inlineStr"/>
       <c r="AF27" t="inlineStr"/>
-      <c r="AG27" t="inlineStr"/>
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t>Revisar: parece comida rapida</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Fullbanqueteria</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>3.9</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>8251256 La Florida, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>9 9307 4817</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>http://www.fullbanqueteria.cl/</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Restaurante</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Fullbanqueteria/data=!4m7!3m6!1s0x9662d0c542546eb9:0xb17a335123f6437e!8m2!3d-33.553252!4d-70.5872741!16s%2Fg%2F11f00m18tl!19sChIJuW5UQsXQYpYRfkP2I1EzerE?authuser=0&amp;hl=es-419&amp;rclk=1</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>-33.553252</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>-70.5872741</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>La Florida</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Google Maps web scraping con Playwright</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr"/>
+      <c r="W28" t="inlineStr"/>
+      <c r="X28" t="inlineStr"/>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr"/>
+      <c r="AA28" t="inlineStr"/>
+      <c r="AB28" t="inlineStr"/>
+      <c r="AC28" t="inlineStr"/>
+      <c r="AD28" t="inlineStr"/>
+      <c r="AE28" t="inlineStr"/>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>La Junta Sandwichera</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Gral Arriagada 371, 8310025 La Florida, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Restaurante</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/La+Junta+Sandwichera/data=!4m7!3m6!1s0x9662d0cedecb5863:0xa81057e194e9dcfa!8m2!3d-33.5576358!4d-70.5908471!16s%2Fg%2F11fy_qst5w!19sChIJY1jL3s7QYpYR-tzplOFXEKg?authuser=0&amp;hl=es-419&amp;rclk=1</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>-33.5576358</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>-70.5908471</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>La Florida</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Google Maps web scraping con Playwright</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Sin teléfono</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr"/>
+      <c r="X29" t="inlineStr"/>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr"/>
+      <c r="AB29" t="inlineStr"/>
+      <c r="AC29" t="inlineStr"/>
+      <c r="AD29" t="inlineStr"/>
+      <c r="AE29" t="inlineStr"/>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="inlineStr">
+        <is>
+          <t>Revisar: parece sandwich; Sin teléfono visible</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Papa John's San José de La Estrella</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>3.4</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Av. Vicuña Mackenna 10427, 8240000 SANTIAGO, La Florida, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>(2) 3303 4427</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>http://www.papajohns.cl/?utm_source=yext-google-my-business&amp;utm_medium=organic-search&amp;utm_campaign=local-listing</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Pizzería</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Papa+John%27s+San+Jos%C3%A9+de+La+Estrella/data=!4m7!3m6!1s0x9662d0c55b6d8e97:0x6184d0697f7e2ac!8m2!3d-33.5535954!4d-70.5871034!16s%2Fg%2F11s59590_8!19sChIJl45tW8XQYpYRrOL3lwZNGAY?authuser=0&amp;hl=es-419&amp;rclk=1</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>-33.5535954</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>-70.5871034</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>La Florida</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Google Maps web scraping con Playwright</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="inlineStr"/>
+      <c r="X30" t="inlineStr"/>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr"/>
+      <c r="AA30" t="inlineStr"/>
+      <c r="AB30" t="inlineStr"/>
+      <c r="AC30" t="inlineStr"/>
+      <c r="AD30" t="inlineStr"/>
+      <c r="AE30" t="inlineStr"/>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Sushi J&amp;J La Florida</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Av. Vicuña Mackenna 10186, 8300590 La Florida, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>9 3490 7915</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>http://www.sushijyj.cl/</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Restaurante</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Sushi+J%26J+La+Florida/data=!4m7!3m6!1s0x9662d1ae87031eb1:0xcb0e7247766a0bba!8m2!3d-33.5500597!4d-70.5868577!16s%2Fg%2F11r4_mc7z_!19sChIJsR4Dh67RYpYRugtqdkdyDss?authuser=0&amp;hl=es-419&amp;rclk=1</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>-33.5500597</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>-70.5868577</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>La Florida</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Google Maps web scraping con Playwright</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="inlineStr"/>
+      <c r="W31" t="inlineStr"/>
+      <c r="X31" t="inlineStr"/>
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="inlineStr"/>
+      <c r="AA31" t="inlineStr"/>
+      <c r="AB31" t="inlineStr"/>
+      <c r="AC31" t="inlineStr"/>
+      <c r="AD31" t="inlineStr"/>
+      <c r="AE31" t="inlineStr"/>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AG27"/>
+  <autoFilter ref="A1:AG31"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>